--- a/data_lake/datos_diarios_preliminares/dt=2026-07-12/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-12/Temp-max-julio-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB03FCB-0472-4676-9113-045CF3F27DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12D7C57-45EF-4F3B-B779-063E4D51853E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9445,7 +9445,9 @@
       <c r="N5" s="57">
         <v>31.1</v>
       </c>
-      <c r="O5" s="57"/>
+      <c r="O5" s="57">
+        <v>31.6</v>
+      </c>
       <c r="P5" s="57"/>
       <c r="Q5" s="57"/>
       <c r="R5" s="57"/>
@@ -9468,7 +9470,7 @@
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>31.1</v>
+        <v>31.6</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9536,7 +9538,9 @@
       <c r="N6" s="57">
         <v>30.4</v>
       </c>
-      <c r="O6" s="57"/>
+      <c r="O6" s="57">
+        <v>31.2</v>
+      </c>
       <c r="P6" s="57"/>
       <c r="Q6" s="57"/>
       <c r="R6" s="57"/>
@@ -9559,7 +9563,7 @@
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9627,7 +9631,9 @@
       <c r="N7" s="57">
         <v>34.200000000000003</v>
       </c>
-      <c r="O7" s="57"/>
+      <c r="O7" s="57">
+        <v>37.200000000000003</v>
+      </c>
       <c r="P7" s="57"/>
       <c r="Q7" s="57"/>
       <c r="R7" s="57"/>
@@ -9650,7 +9656,7 @@
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>34.200000000000003</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9718,7 +9724,9 @@
       <c r="N8" s="57">
         <v>33.6</v>
       </c>
-      <c r="O8" s="57"/>
+      <c r="O8" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="P8" s="57"/>
       <c r="Q8" s="57"/>
       <c r="R8" s="57"/>
@@ -9741,7 +9749,7 @@
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9809,7 +9817,9 @@
       <c r="N9" s="57">
         <v>33.9</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="57">
+        <v>33</v>
+      </c>
       <c r="P9" s="57"/>
       <c r="Q9" s="57"/>
       <c r="R9" s="57"/>
@@ -9832,7 +9842,7 @@
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -9900,7 +9910,9 @@
       <c r="N10" s="57">
         <v>33.9</v>
       </c>
-      <c r="O10" s="57"/>
+      <c r="O10" s="57">
+        <v>35.799999999999997</v>
+      </c>
       <c r="P10" s="57"/>
       <c r="Q10" s="57"/>
       <c r="R10" s="57"/>
@@ -9923,7 +9935,7 @@
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>33.9</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -9991,7 +10003,9 @@
       <c r="N11" s="57">
         <v>37.9</v>
       </c>
-      <c r="O11" s="57"/>
+      <c r="O11" s="57">
+        <v>38</v>
+      </c>
       <c r="P11" s="57"/>
       <c r="Q11" s="57"/>
       <c r="R11" s="57"/>
@@ -10014,7 +10028,7 @@
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10082,7 +10096,9 @@
       <c r="N12" s="57">
         <v>34.6</v>
       </c>
-      <c r="O12" s="57"/>
+      <c r="O12" s="57">
+        <v>34.799999999999997</v>
+      </c>
       <c r="P12" s="57"/>
       <c r="Q12" s="57"/>
       <c r="R12" s="57"/>
@@ -10105,7 +10121,7 @@
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>34.6</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10173,7 +10189,9 @@
       <c r="N13" s="57">
         <v>36.799999999999997</v>
       </c>
-      <c r="O13" s="57"/>
+      <c r="O13" s="57">
+        <v>36.6</v>
+      </c>
       <c r="P13" s="57"/>
       <c r="Q13" s="57"/>
       <c r="R13" s="57"/>
@@ -10196,7 +10214,7 @@
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>36.799999999999997</v>
+        <v>36.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10264,7 +10282,9 @@
       <c r="N14" s="57">
         <v>34.5</v>
       </c>
-      <c r="O14" s="57"/>
+      <c r="O14" s="57">
+        <v>35</v>
+      </c>
       <c r="P14" s="57"/>
       <c r="Q14" s="57"/>
       <c r="R14" s="57"/>
@@ -10287,7 +10307,7 @@
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10355,7 +10375,9 @@
       <c r="N15" s="57">
         <v>32</v>
       </c>
-      <c r="O15" s="57"/>
+      <c r="O15" s="57">
+        <v>32</v>
+      </c>
       <c r="P15" s="57"/>
       <c r="Q15" s="57"/>
       <c r="R15" s="57"/>
@@ -10495,7 +10517,9 @@
       <c r="N17" s="57">
         <v>34.5</v>
       </c>
-      <c r="O17" s="57"/>
+      <c r="O17" s="57">
+        <v>35.4</v>
+      </c>
       <c r="P17" s="57"/>
       <c r="Q17" s="57"/>
       <c r="R17" s="57"/>
@@ -10518,7 +10542,7 @@
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10586,7 +10610,9 @@
       <c r="N18" s="57">
         <v>27.8</v>
       </c>
-      <c r="O18" s="57"/>
+      <c r="O18" s="57">
+        <v>27.4</v>
+      </c>
       <c r="P18" s="57"/>
       <c r="Q18" s="57"/>
       <c r="R18" s="57"/>
@@ -10609,7 +10635,7 @@
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -10677,7 +10703,9 @@
       <c r="N19" s="57">
         <v>34.200000000000003</v>
       </c>
-      <c r="O19" s="57"/>
+      <c r="O19" s="57">
+        <v>33.5</v>
+      </c>
       <c r="P19" s="57"/>
       <c r="Q19" s="57"/>
       <c r="R19" s="57"/>
@@ -10700,7 +10728,7 @@
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>34.200000000000003</v>
+        <v>33.5</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -10768,7 +10796,9 @@
       <c r="N20" s="57">
         <v>30.2</v>
       </c>
-      <c r="O20" s="57"/>
+      <c r="O20" s="57">
+        <v>31.2</v>
+      </c>
       <c r="P20" s="57"/>
       <c r="Q20" s="57"/>
       <c r="R20" s="57"/>
@@ -10791,7 +10821,7 @@
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>30.2</v>
+        <v>31.2</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -10859,7 +10889,9 @@
       <c r="N21" s="57">
         <v>24.1</v>
       </c>
-      <c r="O21" s="57"/>
+      <c r="O21" s="57">
+        <v>24.5</v>
+      </c>
       <c r="P21" s="57"/>
       <c r="Q21" s="57"/>
       <c r="R21" s="57"/>
@@ -10882,7 +10914,7 @@
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11018,7 +11050,9 @@
       <c r="N23" s="57">
         <v>28.8</v>
       </c>
-      <c r="O23" s="57"/>
+      <c r="O23" s="57">
+        <v>26.6</v>
+      </c>
       <c r="P23" s="57"/>
       <c r="Q23" s="57"/>
       <c r="R23" s="57"/>
@@ -11041,7 +11075,7 @@
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>28.8</v>
+        <v>26.6</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11109,7 +11143,9 @@
       <c r="N24" s="57">
         <v>31.6</v>
       </c>
-      <c r="O24" s="57"/>
+      <c r="O24" s="57">
+        <v>29.1</v>
+      </c>
       <c r="P24" s="57"/>
       <c r="Q24" s="57"/>
       <c r="R24" s="57"/>
@@ -11132,7 +11168,7 @@
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>31.6</v>
+        <v>29.1</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11200,7 +11236,9 @@
       <c r="N25" s="57">
         <v>31.2</v>
       </c>
-      <c r="O25" s="57"/>
+      <c r="O25" s="57">
+        <v>31.7</v>
+      </c>
       <c r="P25" s="57"/>
       <c r="Q25" s="57"/>
       <c r="R25" s="57"/>
@@ -11223,7 +11261,7 @@
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>31.7</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11291,7 +11329,9 @@
       <c r="N26" s="57">
         <v>17.899999999999999</v>
       </c>
-      <c r="O26" s="57"/>
+      <c r="O26" s="57">
+        <v>19.399999999999999</v>
+      </c>
       <c r="P26" s="57"/>
       <c r="Q26" s="57"/>
       <c r="R26" s="57"/>
@@ -11314,7 +11354,7 @@
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>17.899999999999999</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11382,7 +11422,9 @@
       <c r="N27" s="57">
         <v>18.100000000000001</v>
       </c>
-      <c r="O27" s="57"/>
+      <c r="O27" s="57">
+        <v>19.5</v>
+      </c>
       <c r="P27" s="57"/>
       <c r="Q27" s="57"/>
       <c r="R27" s="57"/>
@@ -11405,7 +11447,7 @@
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>18.100000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -11473,7 +11515,9 @@
       <c r="N28" s="57">
         <v>32.6</v>
       </c>
-      <c r="O28" s="57"/>
+      <c r="O28" s="57">
+        <v>30.7</v>
+      </c>
       <c r="P28" s="57"/>
       <c r="Q28" s="57"/>
       <c r="R28" s="57"/>
@@ -11496,7 +11540,7 @@
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>30.7</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -11630,7 +11674,9 @@
       <c r="N30" s="57">
         <v>35</v>
       </c>
-      <c r="O30" s="57"/>
+      <c r="O30" s="57">
+        <v>35.799999999999997</v>
+      </c>
       <c r="P30" s="57"/>
       <c r="Q30" s="57"/>
       <c r="R30" s="57"/>
@@ -11653,7 +11699,7 @@
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -11721,7 +11767,9 @@
       <c r="N31" s="57">
         <v>27.5</v>
       </c>
-      <c r="O31" s="57"/>
+      <c r="O31" s="57">
+        <v>27.8</v>
+      </c>
       <c r="P31" s="57"/>
       <c r="Q31" s="57"/>
       <c r="R31" s="57"/>
@@ -11744,7 +11792,7 @@
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -11812,7 +11860,9 @@
       <c r="N32" s="57">
         <v>17.2</v>
       </c>
-      <c r="O32" s="57"/>
+      <c r="O32" s="57">
+        <v>17.8</v>
+      </c>
       <c r="P32" s="57"/>
       <c r="Q32" s="57"/>
       <c r="R32" s="57"/>
@@ -11835,7 +11885,7 @@
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -11903,7 +11953,9 @@
       <c r="N33" s="57">
         <v>15</v>
       </c>
-      <c r="O33" s="57"/>
+      <c r="O33" s="57">
+        <v>15.6</v>
+      </c>
       <c r="P33" s="57"/>
       <c r="Q33" s="57"/>
       <c r="R33" s="57"/>
@@ -11926,7 +11978,7 @@
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12046,7 +12098,9 @@
       <c r="N35" s="57">
         <v>33.4</v>
       </c>
-      <c r="O35" s="57"/>
+      <c r="O35" s="57">
+        <v>30.2</v>
+      </c>
       <c r="P35" s="57"/>
       <c r="Q35" s="57"/>
       <c r="R35" s="57"/>
@@ -12069,7 +12123,7 @@
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>30.2</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -12258,7 +12312,9 @@
       <c r="N38" s="57">
         <v>30.4</v>
       </c>
-      <c r="O38" s="57"/>
+      <c r="O38" s="57">
+        <v>30.1</v>
+      </c>
       <c r="P38" s="57"/>
       <c r="Q38" s="57"/>
       <c r="R38" s="57"/>
@@ -12281,7 +12337,7 @@
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -12350,7 +12406,9 @@
       <c r="N39" s="57">
         <v>29.4</v>
       </c>
-      <c r="O39" s="57"/>
+      <c r="O39" s="57">
+        <v>32.299999999999997</v>
+      </c>
       <c r="P39" s="57"/>
       <c r="Q39" s="57"/>
       <c r="R39" s="57"/>
@@ -12373,18 +12431,18 @@
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>29.4</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="AL39" s="22">
         <v>37.4</v>
       </c>
       <c r="AM39" s="23">
         <f t="shared" si="2"/>
-        <v>-5.3999999999999986</v>
+        <v>-5.1000000000000014</v>
       </c>
       <c r="AN39" s="23">
         <v>30.843133110863921</v>
@@ -12442,7 +12500,9 @@
       <c r="N40" s="57">
         <v>30.6</v>
       </c>
-      <c r="O40" s="57"/>
+      <c r="O40" s="57">
+        <v>30.4</v>
+      </c>
       <c r="P40" s="57"/>
       <c r="Q40" s="57"/>
       <c r="R40" s="57"/>
@@ -12465,7 +12525,7 @@
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -12534,7 +12594,9 @@
       <c r="N41" s="57">
         <v>32</v>
       </c>
-      <c r="O41" s="57"/>
+      <c r="O41" s="57">
+        <v>31.6</v>
+      </c>
       <c r="P41" s="57"/>
       <c r="Q41" s="57"/>
       <c r="R41" s="57"/>
@@ -12557,7 +12619,7 @@
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -12875,7 +12937,9 @@
       <c r="N45" s="57">
         <v>32</v>
       </c>
-      <c r="O45" s="57"/>
+      <c r="O45" s="57">
+        <v>31</v>
+      </c>
       <c r="P45" s="57"/>
       <c r="Q45" s="57"/>
       <c r="R45" s="57"/>
@@ -12898,7 +12962,7 @@
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -13106,7 +13170,9 @@
       <c r="N48" s="57">
         <v>30.4</v>
       </c>
-      <c r="O48" s="57"/>
+      <c r="O48" s="57">
+        <v>27.6</v>
+      </c>
       <c r="P48" s="57"/>
       <c r="Q48" s="57"/>
       <c r="R48" s="57"/>
@@ -13129,7 +13195,7 @@
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>27.6</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -26049,6 +26115,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26058,12 +26130,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
